--- a/data/CReDEs/v4/dg_jc.xlsx
+++ b/data/CReDEs/v4/dg_jc.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\桌面\东肝\CReDEs\new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C0834BB-E36E-443B-91F2-A30A089AA753}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70C3DDC8-AF45-4563-A366-3372359F4BE6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135" xr2:uid="{1C550761-9F7F-481F-BDCB-B9431E97BB7F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="179021"/>
+  <calcPr calcId="179021" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="87">
   <si>
     <t>标签类型</t>
   </si>
@@ -223,10 +223,6 @@
   </si>
   <si>
     <t>肿瘤个数</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -294,10 +290,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>脾脏大小</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>脾门厚度</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -347,6 +339,18 @@
   </si>
   <si>
     <t>string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>请填写以下选项：无，有，未描述，若有则填写转移数，单位为“个”</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>脾脏大小长径</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>请填写符合描述的内容，单位为"cm"，若没有描述则填写"未描述"</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -860,7 +864,7 @@
         <v>53</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -880,7 +884,7 @@
         <v>53</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -916,10 +920,10 @@
         <v>60</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -939,7 +943,7 @@
         <v>10</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -953,13 +957,13 @@
         <v>31</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>53</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -973,13 +977,13 @@
         <v>33</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>53</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -993,13 +997,13 @@
         <v>35</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -1019,7 +1023,7 @@
         <v>53</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1052,13 +1056,13 @@
         <v>12</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
@@ -1072,13 +1076,13 @@
         <v>14</v>
       </c>
       <c r="E14" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
@@ -1092,13 +1096,13 @@
         <v>41</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>53</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
@@ -1112,13 +1116,13 @@
         <v>43</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>53</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
@@ -1132,13 +1136,13 @@
         <v>45</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>53</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
@@ -1152,13 +1156,13 @@
         <v>47</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>53</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
@@ -1169,16 +1173,16 @@
         <v>7</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>53</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
@@ -1192,10 +1196,10 @@
         <v>17</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>57</v>
@@ -1212,10 +1216,10 @@
         <v>50</v>
       </c>
       <c r="E21" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>57</v>
@@ -1232,10 +1236,10 @@
         <v>52</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>57</v>

--- a/data/CReDEs/v4/dg_jc.xlsx
+++ b/data/CReDEs/v4/dg_jc.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\桌面\东肝\CReDEs\new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70C3DDC8-AF45-4563-A366-3372359F4BE6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94882840-8C55-442F-BE32-2A2F1604AC49}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135" xr2:uid="{1C550761-9F7F-481F-BDCB-B9431E97BB7F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="179021" concurrentCalc="0"/>
+  <calcPr calcId="179021"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -318,10 +318,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>请填写符合描述的内容，单位为“个”，若没有描述则填写"未描述"</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>请填写符合描述的内容，单位为“mm”，若没有描述则填写"未描述"</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -351,6 +347,10 @@
   </si>
   <si>
     <t>请填写符合描述的内容，单位为"cm"，若没有描述则填写"未描述"</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>请填写以下选项：无，有，未描述，若有则填写相应的内容，单位为“个”</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -923,7 +923,7 @@
         <v>53</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -1003,7 +1003,7 @@
         <v>53</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -1096,13 +1096,13 @@
         <v>41</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>53</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
@@ -1182,7 +1182,7 @@
         <v>53</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
@@ -1196,7 +1196,7 @@
         <v>17</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>75</v>
@@ -1216,10 +1216,10 @@
         <v>50</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>57</v>
@@ -1236,10 +1236,10 @@
         <v>52</v>
       </c>
       <c r="E22" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>83</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>57</v>

--- a/data/CReDEs/v4/dg_jc.xlsx
+++ b/data/CReDEs/v4/dg_jc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\桌面\东肝\CReDEs\new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94882840-8C55-442F-BE32-2A2F1604AC49}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BBDD7EF-F8EF-43BA-A42F-151B7A247DE2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135" xr2:uid="{1C550761-9F7F-481F-BDCB-B9431E97BB7F}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="88">
   <si>
     <t>标签类型</t>
   </si>
@@ -203,10 +203,6 @@
   </si>
   <si>
     <t>食管胃底静脉曲张标志</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>bool</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -351,6 +347,14 @@
   </si>
   <si>
     <t>请填写以下选项：无，有，未描述，若有则填写相应的内容，单位为“个”</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>请填写以下选项：是，否，未描述,请填写以下选项：是，否，未描述,请填写以下选项：是，否，未描述</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>请填写以下选项：无，轻，中，重，未查，未描述</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -841,10 +845,10 @@
         <v>55</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -858,13 +862,13 @@
         <v>21</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>53</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -878,13 +882,13 @@
         <v>24</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>53</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -917,13 +921,13 @@
         <v>29</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>53</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -943,7 +947,7 @@
         <v>10</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -957,13 +961,13 @@
         <v>31</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>53</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -977,13 +981,13 @@
         <v>33</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>53</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -997,13 +1001,13 @@
         <v>35</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>53</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -1023,7 +1027,7 @@
         <v>53</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1056,13 +1060,13 @@
         <v>12</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
@@ -1076,13 +1080,13 @@
         <v>14</v>
       </c>
       <c r="E14" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
@@ -1096,13 +1100,13 @@
         <v>41</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>53</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
@@ -1116,13 +1120,13 @@
         <v>43</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>53</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
@@ -1136,13 +1140,13 @@
         <v>45</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>53</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
@@ -1156,13 +1160,13 @@
         <v>47</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>53</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
@@ -1173,16 +1177,16 @@
         <v>7</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>53</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
@@ -1196,13 +1200,13 @@
         <v>17</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>57</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
@@ -1216,13 +1220,13 @@
         <v>50</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
@@ -1236,13 +1240,13 @@
         <v>52</v>
       </c>
       <c r="E22" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="G22" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
